--- a/data/trans_camb/P14B23-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P14B23-Clase-trans_camb.xlsx
@@ -513,7 +513,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con enfermedades crónicas discapacitantes de salud mental (trastornos depresivos o ansiedad)</t>
+          <t>Población cuya depresión o ansiedad le limita</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 0,72</t>
+          <t>-2,36; 0,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 2,57</t>
+          <t>-1,24; 2,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 3,27</t>
+          <t>-2,3; 3,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 5,46</t>
+          <t>-0,19; 5,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 1,46</t>
+          <t>-1,51; 1,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,05; 3,26</t>
+          <t>0,22; 3,23</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-90,22; 176,14</t>
+          <t>-91,78; 213,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-60,68; 450,73</t>
+          <t>-62,63; 398,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-66,71; 314,06</t>
+          <t>-64,95; 399,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 609,18</t>
+          <t>-13,85; 496,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-61,38; 152,24</t>
+          <t>-57,22; 160,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 337,11</t>
+          <t>1,24; 375,71</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 1,1</t>
+          <t>-2,66; 1,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 2,52</t>
+          <t>-1,55; 2,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 1,56</t>
+          <t>-3,75; 1,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 6,52</t>
+          <t>0,69; 6,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 0,74</t>
+          <t>-2,44; 0,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 4,03</t>
+          <t>0,33; 3,91</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-87,71; 130,89</t>
+          <t>-87,65; 167,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-51,39; 256,72</t>
+          <t>-54,3; 254,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-75,56; 98,74</t>
+          <t>-76,36; 97,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,82; 368,4</t>
+          <t>5,56; 387,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-68,21; 51,58</t>
+          <t>-68,42; 50,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,39; 235,14</t>
+          <t>7,63; 257,12</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,98; -1,05</t>
+          <t>-5,12; -0,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 1,84</t>
+          <t>-4,37; 2,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 6,57</t>
+          <t>-4,78; 7,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 6,31</t>
+          <t>-3,37; 6,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 0,08</t>
+          <t>-4,36; -0,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 2,2</t>
+          <t>-5,1; 1,87</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-87,24; -25,92</t>
+          <t>-88,72; -19,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-78,22; 47,95</t>
+          <t>-78,32; 55,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-47,65; 102,65</t>
+          <t>-44,91; 120,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-35,73; 101,79</t>
+          <t>-32,11; 97,85</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-65,65; 2,52</t>
+          <t>-64,94; -1,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-65,43; 42,95</t>
+          <t>-65,94; 37,6</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 1,18</t>
+          <t>-1,71; 1,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 3,08</t>
+          <t>-0,24; 3,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 0,72</t>
+          <t>-4,33; 0,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 1,85</t>
+          <t>-5,04; 1,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 0,51</t>
+          <t>-2,34; 0,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 2,0</t>
+          <t>-1,43; 2,01</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-46,6; 56,5</t>
+          <t>-45,59; 60,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 146,79</t>
+          <t>-6,6; 139,28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-50,94; 15,06</t>
+          <t>-51,41; 10,94</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-64,51; 29,53</t>
+          <t>-57,34; 29,69</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-41,8; 14,9</t>
+          <t>-43,57; 11,37</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-21,9; 51,11</t>
+          <t>-27,09; 50,49</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 3,15</t>
+          <t>-0,31; 3,25</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,03; 5,36</t>
+          <t>1,0; 5,49</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 1,62</t>
+          <t>-5,16; 1,44</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 0,89</t>
+          <t>-5,49; 0,88</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 1,29</t>
+          <t>-2,86; 1,18</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 2,1</t>
+          <t>-2,01; 2,07</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-20,43; 347,18</t>
+          <t>-15,07; 405,82</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>33,65; 573,14</t>
+          <t>30,08; 604,32</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-38,71; 17,88</t>
+          <t>-39,04; 15,75</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-44,43; 8,31</t>
+          <t>-42,99; 9,54</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-32,84; 21,07</t>
+          <t>-33,56; 17,9</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-23,28; 32,58</t>
+          <t>-23,48; 32,3</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,96</t>
+          <t>0,0; 1,67</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1,85; 10,23</t>
+          <t>1,94; 10,27</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 1,41</t>
+          <t>-3,68; 1,33</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 1,02</t>
+          <t>-3,9; 0,95</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 0,97</t>
+          <t>-3,07; 1,01</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 1,5</t>
+          <t>-2,69; 1,57</t>
         </is>
       </c>
     </row>
@@ -1497,22 +1497,22 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-33,06; 16,65</t>
+          <t>-33,75; 16,2</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-37,32; 13,07</t>
+          <t>-35,76; 11,3</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-32,93; 14,49</t>
+          <t>-34,14; 15,25</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-30,44; 22,59</t>
+          <t>-31,59; 24,15</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 0,24</t>
+          <t>-1,21; 0,26</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 2,08</t>
+          <t>0,07; 2,14</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,57; -0,01</t>
+          <t>-2,68; -0,02</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 0,53</t>
+          <t>-2,39; 0,6</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,62; -0,18</t>
+          <t>-1,68; -0,18</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 1,11</t>
+          <t>-0,64; 1,07</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-43,47; 12,7</t>
+          <t>-42,83; 12,65</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>0,12; 96,78</t>
+          <t>2,19; 103,89</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-30,43; -0,21</t>
+          <t>-30,96; -0,26</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-27,07; 6,76</t>
+          <t>-27,69; 7,8</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-28,33; -3,38</t>
+          <t>-29,09; -3,48</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-11,96; 22,23</t>
+          <t>-11,88; 21,4</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P14B23-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P14B23-Clase-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,67</t>
+          <t>0,6</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,85</t>
+          <t>3,04</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,74</t>
+          <t>1,79</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 0,86</t>
+          <t>-2,15; 0,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 2,37</t>
+          <t>-1,34; 2,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 3,33</t>
+          <t>-2,58; 3,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 5,19</t>
+          <t>0,34; 5,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 1,49</t>
+          <t>-1,54; 1,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 3,23</t>
+          <t>0,06; 3,33</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>126,03%</t>
+          <t>134,39%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>102,77%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-91,78; 213,89</t>
+          <t>-90,88; 180,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-62,63; 398,81</t>
+          <t>-58,54; 419,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-64,95; 399,77</t>
+          <t>-67,3; 294,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,85; 496,92</t>
+          <t>-1,89; 672,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-57,22; 160,95</t>
+          <t>-58,51; 139,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 375,71</t>
+          <t>-2,95; 327,44</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,63</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,7</t>
+          <t>3,78</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,05</t>
+          <t>2,08</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 1,1</t>
+          <t>-2,67; 1,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 2,52</t>
+          <t>-1,68; 2,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 1,52</t>
+          <t>-3,63; 1,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 6,8</t>
+          <t>0,76; 6,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 0,8</t>
+          <t>-2,29; 0,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,91</t>
+          <t>0,35; 3,93</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>114,4%</t>
+          <t>116,62%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>82,33%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-87,65; 167,67</t>
+          <t>-87,38; 171,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-54,3; 254,72</t>
+          <t>-59,12; 259,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-76,36; 97,25</t>
+          <t>-76,26; 112,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,56; 387,16</t>
+          <t>6,04; 355,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-68,42; 50,31</t>
+          <t>-66,5; 57,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,63; 257,12</t>
+          <t>4,15; 231,12</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-0,87</t>
+          <t>0,66</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,56</t>
+          <t>1,65</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,79</t>
+          <t>0,91</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,12; -0,89</t>
+          <t>-4,87; -1,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 2,06</t>
+          <t>-1,92; 3,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 7,18</t>
+          <t>-4,86; 7,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 6,22</t>
+          <t>-3,24; 7,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,36; -0,17</t>
+          <t>-4,29; -0,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 1,87</t>
+          <t>-1,46; 3,33</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-20,47%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-14,25%</t>
+          <t>16,43%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-88,72; -19,89</t>
+          <t>-87,9; -26,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-78,32; 55,96</t>
+          <t>-36,62; 106,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-44,91; 120,71</t>
+          <t>-46,5; 123,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-32,11; 97,85</t>
+          <t>-30,74; 110,47</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-64,94; -1,26</t>
+          <t>-65,03; 1,92</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-65,94; 37,6</t>
+          <t>-23,32; 71,24</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,44</t>
+          <t>1,56</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1,03</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,6</t>
+          <t>1,35</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 1,21</t>
+          <t>-1,68; 1,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 3,11</t>
+          <t>0,07; 3,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 0,54</t>
+          <t>-4,07; 0,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 1,79</t>
+          <t>-1,88; 3,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 0,39</t>
+          <t>-2,07; 0,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 2,01</t>
+          <t>-0,09; 2,66</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-14,93%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>30,15%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-45,59; 60,03</t>
+          <t>-47,42; 49,91</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 139,28</t>
+          <t>-0,52; 141,79</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-51,41; 10,94</t>
+          <t>-51,0; 14,17</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-57,34; 29,69</t>
+          <t>-22,24; 53,66</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-43,57; 11,37</t>
+          <t>-40,66; 13,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-27,09; 50,49</t>
+          <t>-1,75; 71,01</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3,07</t>
+          <t>2,6</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-2,13</t>
+          <t>-1,04</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>0,4</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 3,25</t>
+          <t>-0,36; 3,1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,0; 5,49</t>
+          <t>0,53; 4,72</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 1,44</t>
+          <t>-4,77; 1,78</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 0,88</t>
+          <t>-3,95; 1,66</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 1,18</t>
+          <t>-2,86; 1,23</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 2,07</t>
+          <t>-1,64; 2,22</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>179,5%</t>
+          <t>151,89%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-19,0%</t>
+          <t>-9,26%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -1331,39 +1331,39 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-15,07; 405,82</t>
+          <t>-21,23; 351,31</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>30,08; 604,32</t>
+          <t>19,1; 572,12</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-39,04; 15,75</t>
+          <t>-36,98; 18,04</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-42,99; 9,54</t>
+          <t>-30,07; 16,85</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-33,56; 17,9</t>
+          <t>-33,17; 19,56</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-23,48; 32,3</t>
+          <t>-18,65; 35,64</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4,44</t>
+          <t>4,47</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-1,59</t>
+          <t>-1,71</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-0,59</t>
+          <t>-0,6</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,67</t>
+          <t>0,0; 1,41</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1,94; 10,27</t>
+          <t>1,9; 9,92</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 1,33</t>
+          <t>-3,88; 1,24</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 0,95</t>
+          <t>-4,13; 0,83</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 1,01</t>
+          <t>-3,21; 0,85</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 1,57</t>
+          <t>-2,63; 1,72</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-16,51%</t>
+          <t>-17,72%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-7,57%</t>
+          <t>-7,7%</t>
         </is>
       </c>
     </row>
@@ -1497,22 +1497,22 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-33,75; 16,2</t>
+          <t>-34,38; 15,25</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-35,76; 11,3</t>
+          <t>-37,69; 11,17</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-34,14; 15,25</t>
+          <t>-36,02; 11,88</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-31,59; 24,15</t>
+          <t>-29,65; 24,99</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1,21</t>
+          <t>1,39</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-0,74</t>
+          <t>-0,02</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,24</t>
+          <t>0,7</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 0,26</t>
+          <t>-1,29; 0,2</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,07; 2,14</t>
+          <t>0,58; 2,29</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,68; -0,02</t>
+          <t>-2,6; 0,03</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 0,6</t>
+          <t>-1,39; 1,1</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,68; -0,18</t>
+          <t>-1,64; -0,18</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,07</t>
+          <t>-0,12; 1,34</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>57,27%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-9,19%</t>
+          <t>-0,19%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>13,19%</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-42,83; 12,65</t>
+          <t>-43,17; 10,9</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>2,19; 103,89</t>
+          <t>19,7; 108,96</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-30,96; -0,26</t>
+          <t>-29,97; 0,29</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-27,69; 7,8</t>
+          <t>-15,27; 15,23</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-29,09; -3,48</t>
+          <t>-28,56; -3,15</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-11,88; 21,4</t>
+          <t>-2,16; 27,22</t>
         </is>
       </c>
     </row>
